--- a/data/hospital/data.xlsx
+++ b/data/hospital/data.xlsx
@@ -12034,7 +12034,7 @@
         <v>087-811-5588</v>
       </c>
       <c r="L233" t="str">
-        <v>内科、脳神経外科、整形外科、リハビリ科、放射線科、消化器内科</v>
+        <v>内科、皮膚科、脳神経外科、整形外科、リハビリ科、放射線科、消化器内科</v>
       </c>
       <c r="M233" t="str">
         <v/>
